--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A781B3DC-B541-4E9A-ABDD-177B5AE6A997}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03E5AC14-A291-494E-B2B2-9F69C2C61821}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="82">
   <si>
     <t>Día</t>
   </si>
@@ -246,13 +246,34 @@
   </si>
   <si>
     <t>Arroz con maicitos</t>
+  </si>
+  <si>
+    <t>27 jul</t>
+  </si>
+  <si>
+    <t>28 jul</t>
+  </si>
+  <si>
+    <t>29 jul</t>
+  </si>
+  <si>
+    <t>30 jul</t>
+  </si>
+  <si>
+    <t>31 jul</t>
+  </si>
+  <si>
+    <t>1 ago</t>
+  </si>
+  <si>
+    <t>2 ago</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,6 +307,12 @@
       <color rgb="FF4A3524"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -351,7 +378,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -369,6 +396,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -690,8 +721,8 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8">
-        <v>46230</v>
+      <c r="B2" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>7</v>
@@ -706,8 +737,8 @@
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8">
-        <v>46230</v>
+      <c r="B3" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
@@ -722,8 +753,8 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8">
-        <v>46230</v>
+      <c r="B4" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -738,8 +769,8 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8">
-        <v>46230</v>
+      <c r="B5" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
@@ -754,8 +785,8 @@
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8">
-        <v>46230</v>
+      <c r="B6" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -770,8 +801,8 @@
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="8">
-        <v>46231</v>
+      <c r="B7" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
@@ -786,8 +817,8 @@
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8">
-        <v>46231</v>
+      <c r="B8" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
@@ -802,8 +833,8 @@
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="8">
-        <v>46231</v>
+      <c r="B9" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
@@ -818,8 +849,8 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
-        <v>46231</v>
+      <c r="B10" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
@@ -834,8 +865,8 @@
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="8">
-        <v>46231</v>
+      <c r="B11" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
@@ -850,8 +881,8 @@
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="8">
-        <v>46232</v>
+      <c r="B12" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
@@ -870,8 +901,8 @@
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="8">
-        <v>46232</v>
+      <c r="B13" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
@@ -890,8 +921,8 @@
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="8">
-        <v>46232</v>
+      <c r="B14" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
@@ -910,8 +941,8 @@
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="8">
-        <v>46232</v>
+      <c r="B15" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>10</v>
@@ -930,8 +961,8 @@
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="8">
-        <v>46232</v>
+      <c r="B16" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
@@ -948,8 +979,8 @@
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="8">
-        <v>46232</v>
+      <c r="B17" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>10</v>
@@ -968,8 +999,8 @@
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="8">
-        <v>46232</v>
+      <c r="B18" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
@@ -986,8 +1017,8 @@
       <c r="A19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="8">
-        <v>46232</v>
+      <c r="B19" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>10</v>
@@ -1004,8 +1035,8 @@
       <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="8">
-        <v>46232</v>
+      <c r="B20" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>10</v>
@@ -1022,8 +1053,8 @@
       <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="8">
-        <v>46232</v>
+      <c r="B21" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>10</v>
@@ -1040,8 +1071,8 @@
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="8">
-        <v>46233</v>
+      <c r="B22" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>10</v>
@@ -1056,8 +1087,8 @@
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="8">
-        <v>46233</v>
+      <c r="B23" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
@@ -1072,8 +1103,8 @@
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="8">
-        <v>46233</v>
+      <c r="B24" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>10</v>
@@ -1088,8 +1119,8 @@
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="8">
-        <v>46233</v>
+      <c r="B25" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>10</v>
@@ -1104,8 +1135,8 @@
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="8">
-        <v>46233</v>
+      <c r="B26" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>10</v>
@@ -1120,8 +1151,8 @@
       <c r="A27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="8">
-        <v>46234</v>
+      <c r="B27" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>10</v>
@@ -1136,8 +1167,8 @@
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="8">
-        <v>46234</v>
+      <c r="B28" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>10</v>
@@ -1152,8 +1183,8 @@
       <c r="A29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="8">
-        <v>46234</v>
+      <c r="B29" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
@@ -1168,8 +1199,8 @@
       <c r="A30" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="8">
-        <v>46234</v>
+      <c r="B30" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
@@ -1184,8 +1215,8 @@
       <c r="A31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="8">
-        <v>46234</v>
+      <c r="B31" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
@@ -1198,8 +1229,8 @@
       <c r="A32" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="8">
-        <v>46235</v>
+      <c r="B32" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
@@ -1218,8 +1249,8 @@
       <c r="A33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="8">
-        <v>46235</v>
+      <c r="B33" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
@@ -1236,8 +1267,8 @@
       <c r="A34" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="8">
-        <v>46235</v>
+      <c r="B34" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
@@ -1254,8 +1285,8 @@
       <c r="A35" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="8">
-        <v>46235</v>
+      <c r="B35" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
@@ -1272,8 +1303,8 @@
       <c r="A36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="8">
-        <v>46235</v>
+      <c r="B36" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>10</v>
@@ -1290,8 +1321,8 @@
       <c r="A37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="8">
-        <v>46235</v>
+      <c r="B37" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>10</v>
@@ -1308,8 +1339,8 @@
       <c r="A38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="8">
-        <v>46235</v>
+      <c r="B38" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>10</v>
@@ -1326,8 +1357,8 @@
       <c r="A39" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="8">
-        <v>46235</v>
+      <c r="B39" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>10</v>
@@ -1344,8 +1375,8 @@
       <c r="A40" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="8">
-        <v>46235</v>
+      <c r="B40" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>10</v>
@@ -1362,8 +1393,8 @@
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="8">
-        <v>46236</v>
+      <c r="B41" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>10</v>
@@ -1378,8 +1409,8 @@
       <c r="A42" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="8">
-        <v>46236</v>
+      <c r="B42" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>10</v>
@@ -1394,8 +1425,8 @@
       <c r="A43" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="8">
-        <v>46236</v>
+      <c r="B43" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>10</v>
@@ -1410,8 +1441,8 @@
       <c r="A44" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="8">
-        <v>46236</v>
+      <c r="B44" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>10</v>
@@ -1426,8 +1457,8 @@
       <c r="A45" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="8">
-        <v>46236</v>
+      <c r="B45" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>10</v>
@@ -1439,6 +1470,7 @@
       <c r="F45" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="A2:A405" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03E5AC14-A291-494E-B2B2-9F69C2C61821}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6780B3B3-68D6-416C-AF32-9059DEB52C27}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="76">
   <si>
     <t>Día</t>
   </si>
@@ -56,33 +56,9 @@
     <t>No</t>
   </si>
   <si>
-    <t>Sopa de torrejas</t>
-  </si>
-  <si>
-    <t>Guacamole</t>
-  </si>
-  <si>
     <t>Miércoles</t>
   </si>
   <si>
-    <t>Al estilo madrileño</t>
-  </si>
-  <si>
-    <t>Res en salsa de pimienta</t>
-  </si>
-  <si>
-    <t>Con papa y huevo</t>
-  </si>
-  <si>
-    <t>Lechuga romana fresca</t>
-  </si>
-  <si>
-    <t>Arroz almendrado</t>
-  </si>
-  <si>
-    <t>Con almendras tostadas</t>
-  </si>
-  <si>
     <t>Jueves</t>
   </si>
   <si>
@@ -113,15 +89,6 @@
     <t>Sopa de ajiaco</t>
   </si>
   <si>
-    <t>Carne de res / Pollo / Chuleta de cerdo</t>
-  </si>
-  <si>
-    <t>Yuca a la criolla</t>
-  </si>
-  <si>
-    <t>Ensalada fantasía</t>
-  </si>
-  <si>
     <t>Domingo</t>
   </si>
   <si>
@@ -167,106 +134,121 @@
     <t>Sopa de avena</t>
   </si>
   <si>
-    <t>Muchacho relleno en salsa de maracuyá</t>
-  </si>
-  <si>
-    <t>Papa al gratín</t>
-  </si>
-  <si>
-    <t>Ensalada al pesto</t>
-  </si>
-  <si>
-    <t>Pollo a la jardinera</t>
-  </si>
-  <si>
-    <t>Torta de banano</t>
-  </si>
-  <si>
-    <t>Tomate, pepino cohombro y zuccinni a la vinagreta</t>
-  </si>
-  <si>
-    <t>Arroz blando</t>
-  </si>
-  <si>
-    <t>Consomé</t>
-  </si>
-  <si>
-    <t>Costilla de res</t>
-  </si>
-  <si>
-    <t>Yuca, plátano y mazorca</t>
-  </si>
-  <si>
-    <t>Sopa de arracacha</t>
-  </si>
-  <si>
-    <t>Yuca o plátano</t>
-  </si>
-  <si>
-    <t>Sopa de conchitas</t>
-  </si>
-  <si>
-    <t>Pollo a la vizcaína</t>
-  </si>
-  <si>
-    <t>Copitos de papa al cebollín</t>
-  </si>
-  <si>
     <t>Ensalada de melón con vinagreta oriental</t>
   </si>
   <si>
-    <t>Arroz con quinoa</t>
-  </si>
-  <si>
-    <t>Sopa de mazorca</t>
-  </si>
-  <si>
-    <t>Arroz cubano</t>
-  </si>
-  <si>
-    <t>Patacón</t>
-  </si>
-  <si>
-    <t>Ensalada bellavista</t>
-  </si>
-  <si>
-    <t>Hígado a la plancha</t>
-  </si>
-  <si>
-    <t>Sopa de tortilla de huevo</t>
-  </si>
-  <si>
-    <t>Mojarra frita</t>
-  </si>
-  <si>
-    <t>Patacón con hogao</t>
-  </si>
-  <si>
-    <t>Ensalada con aguacate</t>
-  </si>
-  <si>
-    <t>Arroz con maicitos</t>
-  </si>
-  <si>
-    <t>27 jul</t>
-  </si>
-  <si>
-    <t>28 jul</t>
-  </si>
-  <si>
-    <t>29 jul</t>
-  </si>
-  <si>
-    <t>30 jul</t>
-  </si>
-  <si>
-    <t>31 jul</t>
-  </si>
-  <si>
-    <t>1 ago</t>
-  </si>
-  <si>
-    <t>2 ago</t>
+    <t>Sopa de cascabeles</t>
+  </si>
+  <si>
+    <t>Goulash</t>
+  </si>
+  <si>
+    <t>Puré de papa</t>
+  </si>
+  <si>
+    <t>Habichuelas bacon</t>
+  </si>
+  <si>
+    <t>Crema de tomate</t>
+  </si>
+  <si>
+    <t>Fajitas de pollo</t>
+  </si>
+  <si>
+    <t>Fríjoles</t>
+  </si>
+  <si>
+    <t>Ensalada pico e gallo</t>
+  </si>
+  <si>
+    <t>Arroz amarillo</t>
+  </si>
+  <si>
+    <t>3 ago</t>
+  </si>
+  <si>
+    <t>4 ago</t>
+  </si>
+  <si>
+    <t>5 ago</t>
+  </si>
+  <si>
+    <t>6 ago</t>
+  </si>
+  <si>
+    <t>7 ago</t>
+  </si>
+  <si>
+    <t>8 ago</t>
+  </si>
+  <si>
+    <t>9 ago</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco de cebada</t>
+  </si>
+  <si>
+    <t>Pulpa de cerdo a la plancha</t>
+  </si>
+  <si>
+    <t>Papa criolla dorada</t>
+  </si>
+  <si>
+    <t>Ensalada multicolor</t>
+  </si>
+  <si>
+    <t>Sopa de verduras</t>
+  </si>
+  <si>
+    <t>Pechuga rellena con queso y espinaca</t>
+  </si>
+  <si>
+    <t>En salsa miel mostaza</t>
+  </si>
+  <si>
+    <t>Papa crisper</t>
+  </si>
+  <si>
+    <t>Arroz a las finas hierbas</t>
+  </si>
+  <si>
+    <t>Sopa de colicero</t>
+  </si>
+  <si>
+    <t>Carne al vino</t>
+  </si>
+  <si>
+    <t>Croquetas de papa</t>
+  </si>
+  <si>
+    <t>Ensalada waldorf</t>
+  </si>
+  <si>
+    <t>Arroz verde</t>
+  </si>
+  <si>
+    <t>Soufflé de pollo y atún</t>
+  </si>
+  <si>
+    <t>Papa chip</t>
+  </si>
+  <si>
+    <t>Ensalada al huevo</t>
+  </si>
+  <si>
+    <t>Lomo de cerdo</t>
+  </si>
+  <si>
+    <t>Papa Lyonesa</t>
+  </si>
+  <si>
+    <t>Ensalada verde</t>
+  </si>
+  <si>
+    <t>Arroz con ajonjolí</t>
+  </si>
+  <si>
+    <t>En salsa de maracuyá</t>
   </si>
 </sst>
 </file>
@@ -687,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -722,14 +704,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -738,14 +720,14 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -754,14 +736,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -770,14 +752,14 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -786,14 +768,14 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -802,14 +784,14 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -818,14 +800,14 @@
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -834,30 +816,30 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -866,110 +848,92 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>14</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="4" t="s">
         <v>8</v>
       </c>
@@ -977,322 +941,323 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="4"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E27" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E28" s="4" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E29" s="4" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E30" s="4" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>25</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>8</v>
@@ -1304,16 +1269,14 @@
         <v>22</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F36" s="4"/>
     </row>
@@ -1322,34 +1285,32 @@
         <v>22</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F37" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F38" s="4"/>
     </row>
@@ -1358,16 +1319,14 @@
         <v>22</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F39" s="4"/>
     </row>
@@ -1376,109 +1335,27 @@
         <v>22</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D40" s="3"/>
       <c r="E40" s="4" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="F40" s="4"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41" s="4"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F42" s="4"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F43" s="4"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F44" s="4"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F45" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A405" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C405" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D405" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1496,7 +1373,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1504,7 +1381,7 @@
     </row>
     <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -1512,32 +1389,32 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -1545,12 +1422,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -1558,17 +1435,17 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6780B3B3-68D6-416C-AF32-9059DEB52C27}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D5B9238-A76D-45ED-B208-445F423D1B4D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -134,9 +134,6 @@
     <t>Sopa de avena</t>
   </si>
   <si>
-    <t>Ensalada de melón con vinagreta oriental</t>
-  </si>
-  <si>
     <t>Sopa de cascabeles</t>
   </si>
   <si>
@@ -249,6 +246,9 @@
   </si>
   <si>
     <t>En salsa de maracuyá</t>
+  </si>
+  <si>
+    <t>Ensalada césar</t>
   </si>
 </sst>
 </file>
@@ -704,14 +704,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -720,14 +720,14 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -736,14 +736,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -752,14 +752,14 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -768,7 +768,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -784,14 +784,14 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -800,14 +800,14 @@
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -816,14 +816,14 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -832,14 +832,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -848,14 +848,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -864,14 +864,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -880,14 +880,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -896,14 +896,14 @@
         <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" s="4"/>
     </row>
@@ -912,14 +912,14 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F15" s="4"/>
     </row>
@@ -928,7 +928,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
@@ -944,14 +944,14 @@
         <v>12</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -960,17 +960,17 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -978,14 +978,14 @@
         <v>12</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -994,14 +994,14 @@
         <v>12</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="F20" s="4"/>
     </row>
@@ -1010,14 +1010,14 @@
         <v>12</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1025,14 +1025,14 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F22" s="4"/>
     </row>
@@ -1041,14 +1041,14 @@
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -1057,14 +1057,14 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1073,14 +1073,14 @@
         <v>13</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -1089,14 +1089,14 @@
         <v>13</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F26" s="4"/>
     </row>
@@ -1105,7 +1105,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>10</v>
@@ -1125,7 +1125,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>10</v>
@@ -1143,7 +1143,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
@@ -1161,7 +1161,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
@@ -1197,7 +1197,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
@@ -1206,7 +1206,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F32" s="4"/>
     </row>
@@ -1215,7 +1215,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F33" s="4"/>
     </row>
@@ -1233,7 +1233,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
@@ -1242,7 +1242,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F34" s="4"/>
     </row>
@@ -1251,7 +1251,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
@@ -1269,7 +1269,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>10</v>
@@ -1285,17 +1285,17 @@
         <v>22</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1303,14 +1303,14 @@
         <v>22</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F38" s="4"/>
     </row>
@@ -1319,14 +1319,14 @@
         <v>22</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F39" s="4"/>
     </row>
@@ -1335,14 +1335,14 @@
         <v>22</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F40" s="4"/>
     </row>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D5B9238-A76D-45ED-B208-445F423D1B4D}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80AB9747-3789-420C-A31B-3B30BF417F58}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -707,7 +707,7 @@
         <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
@@ -723,7 +723,7 @@
         <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
@@ -739,7 +739,7 @@
         <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
@@ -755,7 +755,7 @@
         <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
@@ -771,7 +771,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80AB9747-3789-420C-A31B-3B30BF417F58}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B4FF3AF-7726-44C2-B6EC-250E6686E41B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="75">
   <si>
     <t>Día</t>
   </si>
@@ -131,124 +131,121 @@
     <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
   </si>
   <si>
-    <t>Sopa de avena</t>
-  </si>
-  <si>
-    <t>Sopa de cascabeles</t>
-  </si>
-  <si>
-    <t>Goulash</t>
-  </si>
-  <si>
-    <t>Puré de papa</t>
-  </si>
-  <si>
-    <t>Habichuelas bacon</t>
-  </si>
-  <si>
-    <t>Crema de tomate</t>
-  </si>
-  <si>
-    <t>Fajitas de pollo</t>
-  </si>
-  <si>
-    <t>Fríjoles</t>
-  </si>
-  <si>
-    <t>Ensalada pico e gallo</t>
-  </si>
-  <si>
-    <t>Arroz amarillo</t>
-  </si>
-  <si>
-    <t>3 ago</t>
-  </si>
-  <si>
-    <t>4 ago</t>
-  </si>
-  <si>
-    <t>5 ago</t>
-  </si>
-  <si>
-    <t>6 ago</t>
-  </si>
-  <si>
-    <t>7 ago</t>
-  </si>
-  <si>
-    <t>8 ago</t>
-  </si>
-  <si>
-    <t>9 ago</t>
-  </si>
-  <si>
-    <t>Sopa de cuchuco de cebada</t>
-  </si>
-  <si>
-    <t>Pulpa de cerdo a la plancha</t>
-  </si>
-  <si>
-    <t>Papa criolla dorada</t>
-  </si>
-  <si>
-    <t>Ensalada multicolor</t>
-  </si>
-  <si>
-    <t>Sopa de verduras</t>
-  </si>
-  <si>
-    <t>Pechuga rellena con queso y espinaca</t>
-  </si>
-  <si>
-    <t>En salsa miel mostaza</t>
-  </si>
-  <si>
-    <t>Papa crisper</t>
-  </si>
-  <si>
-    <t>Arroz a las finas hierbas</t>
-  </si>
-  <si>
-    <t>Sopa de colicero</t>
-  </si>
-  <si>
-    <t>Carne al vino</t>
-  </si>
-  <si>
-    <t>Croquetas de papa</t>
-  </si>
-  <si>
-    <t>Ensalada waldorf</t>
-  </si>
-  <si>
-    <t>Arroz verde</t>
-  </si>
-  <si>
-    <t>Soufflé de pollo y atún</t>
-  </si>
-  <si>
-    <t>Papa chip</t>
-  </si>
-  <si>
-    <t>Ensalada al huevo</t>
-  </si>
-  <si>
-    <t>Lomo de cerdo</t>
-  </si>
-  <si>
-    <t>Papa Lyonesa</t>
-  </si>
-  <si>
-    <t>Ensalada verde</t>
-  </si>
-  <si>
-    <t>Arroz con ajonjolí</t>
-  </si>
-  <si>
-    <t>En salsa de maracuyá</t>
-  </si>
-  <si>
-    <t>Ensalada césar</t>
+    <t>10 ago</t>
+  </si>
+  <si>
+    <t>11 ago</t>
+  </si>
+  <si>
+    <t>12 ago</t>
+  </si>
+  <si>
+    <t>13 ago</t>
+  </si>
+  <si>
+    <t>14 ago</t>
+  </si>
+  <si>
+    <t>15 ago</t>
+  </si>
+  <si>
+    <t>16 ago</t>
+  </si>
+  <si>
+    <t>Sopa de mute</t>
+  </si>
+  <si>
+    <t>Sobrebarriga al horno</t>
+  </si>
+  <si>
+    <t>Papa chorreada</t>
+  </si>
+  <si>
+    <t>Ensalada con aguacate</t>
+  </si>
+  <si>
+    <t>Sopa de cebada perlada</t>
+  </si>
+  <si>
+    <t>Pollo oriental</t>
+  </si>
+  <si>
+    <t>En salsa de mango</t>
+  </si>
+  <si>
+    <t>Copitos de papa al cebollín</t>
+  </si>
+  <si>
+    <t>Ensalada mediterránea</t>
+  </si>
+  <si>
+    <t>Arroz al perejil</t>
+  </si>
+  <si>
+    <t>Sopa de lentejas</t>
+  </si>
+  <si>
+    <t>Chuleta de cerdo apanada</t>
+  </si>
+  <si>
+    <t>Mini yuca dorada</t>
+  </si>
+  <si>
+    <t>Ensalada oriental</t>
+  </si>
+  <si>
+    <t>Sopa de pasta</t>
+  </si>
+  <si>
+    <t>Arroz con pollo</t>
+  </si>
+  <si>
+    <t>Plátano al horno</t>
+  </si>
+  <si>
+    <t>Ensalada de pepino cohombro con yogurt</t>
+  </si>
+  <si>
+    <t>Sopa de sancocho</t>
+  </si>
+  <si>
+    <t>Filete de mojarra</t>
+  </si>
+  <si>
+    <t>En salsa de camarones</t>
+  </si>
+  <si>
+    <t>Enyucado</t>
+  </si>
+  <si>
+    <t>Arroz con maicitos</t>
+  </si>
+  <si>
+    <t>Lengua a la criolla</t>
+  </si>
+  <si>
+    <t>Purpe de papa mixto</t>
+  </si>
+  <si>
+    <t>Ensalada arcoíris</t>
+  </si>
+  <si>
+    <t>Crema de apio</t>
+  </si>
+  <si>
+    <t>Piccata de pollo</t>
+  </si>
+  <si>
+    <t>Pasta corta con tomates frescos</t>
+  </si>
+  <si>
+    <t>Ensalada de melón</t>
+  </si>
+  <si>
+    <t>Con vinagreta oriental</t>
+  </si>
+  <si>
+    <t>Arroz al cebollín</t>
   </si>
 </sst>
 </file>
@@ -669,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -704,14 +701,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -720,14 +717,14 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -736,14 +733,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -752,14 +749,14 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -768,7 +765,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>10</v>
@@ -784,14 +781,14 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -800,30 +797,32 @@
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -832,14 +831,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -848,14 +847,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -864,7 +863,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
@@ -880,7 +879,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
@@ -896,7 +895,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
@@ -912,7 +911,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>10</v>
@@ -928,7 +927,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
@@ -944,7 +943,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>10</v>
@@ -960,7 +959,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
@@ -969,23 +968,21 @@
       <c r="E18" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -994,38 +991,39 @@
         <v>12</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>7</v>
@@ -1034,21 +1032,23 @@
       <c r="E22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -1057,14 +1057,14 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1073,7 +1073,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
@@ -1086,26 +1086,30 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E26" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>10</v>
@@ -1114,18 +1118,16 @@
         <v>15</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>10</v>
@@ -1134,7 +1136,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F28" s="4"/>
     </row>
@@ -1143,7 +1145,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
@@ -1152,7 +1154,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F29" s="4"/>
     </row>
@@ -1161,16 +1163,16 @@
         <v>14</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F30" s="4"/>
     </row>
@@ -1179,7 +1181,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
@@ -1188,7 +1190,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="F31" s="4"/>
     </row>
@@ -1197,7 +1199,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
@@ -1215,7 +1217,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
@@ -1233,7 +1235,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
@@ -1242,25 +1244,23 @@
         <v>20</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D35" s="3"/>
       <c r="E35" s="4" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="F35" s="4"/>
     </row>
@@ -1269,14 +1269,14 @@
         <v>22</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="F36" s="4"/>
     </row>
@@ -1285,77 +1285,61 @@
         <v>22</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F38" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F39" s="4"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F40" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A399" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C399" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D399" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B4FF3AF-7726-44C2-B6EC-250E6686E41B}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005E44FE-CDE7-44E5-A1E0-A5F4FEA6F867}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="79">
   <si>
     <t>Día</t>
   </si>
@@ -131,121 +131,133 @@
     <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
   </si>
   <si>
-    <t>10 ago</t>
-  </si>
-  <si>
-    <t>11 ago</t>
-  </si>
-  <si>
-    <t>12 ago</t>
-  </si>
-  <si>
-    <t>13 ago</t>
-  </si>
-  <si>
-    <t>14 ago</t>
-  </si>
-  <si>
-    <t>15 ago</t>
-  </si>
-  <si>
-    <t>16 ago</t>
-  </si>
-  <si>
     <t>Sopa de mute</t>
   </si>
   <si>
-    <t>Sobrebarriga al horno</t>
-  </si>
-  <si>
-    <t>Papa chorreada</t>
-  </si>
-  <si>
-    <t>Ensalada con aguacate</t>
-  </si>
-  <si>
-    <t>Sopa de cebada perlada</t>
-  </si>
-  <si>
-    <t>Pollo oriental</t>
-  </si>
-  <si>
-    <t>En salsa de mango</t>
-  </si>
-  <si>
-    <t>Copitos de papa al cebollín</t>
-  </si>
-  <si>
-    <t>Ensalada mediterránea</t>
-  </si>
-  <si>
-    <t>Arroz al perejil</t>
-  </si>
-  <si>
-    <t>Sopa de lentejas</t>
-  </si>
-  <si>
-    <t>Chuleta de cerdo apanada</t>
-  </si>
-  <si>
-    <t>Mini yuca dorada</t>
-  </si>
-  <si>
-    <t>Ensalada oriental</t>
-  </si>
-  <si>
-    <t>Sopa de pasta</t>
-  </si>
-  <si>
-    <t>Arroz con pollo</t>
-  </si>
-  <si>
-    <t>Plátano al horno</t>
-  </si>
-  <si>
-    <t>Ensalada de pepino cohombro con yogurt</t>
-  </si>
-  <si>
-    <t>Sopa de sancocho</t>
-  </si>
-  <si>
-    <t>Filete de mojarra</t>
-  </si>
-  <si>
-    <t>En salsa de camarones</t>
-  </si>
-  <si>
-    <t>Enyucado</t>
-  </si>
-  <si>
-    <t>Arroz con maicitos</t>
-  </si>
-  <si>
-    <t>Lengua a la criolla</t>
-  </si>
-  <si>
-    <t>Purpe de papa mixto</t>
-  </si>
-  <si>
-    <t>Ensalada arcoíris</t>
-  </si>
-  <si>
-    <t>Crema de apio</t>
-  </si>
-  <si>
-    <t>Piccata de pollo</t>
-  </si>
-  <si>
-    <t>Pasta corta con tomates frescos</t>
-  </si>
-  <si>
-    <t>Ensalada de melón</t>
-  </si>
-  <si>
-    <t>Con vinagreta oriental</t>
-  </si>
-  <si>
     <t>Arroz al cebollín</t>
+  </si>
+  <si>
+    <t>17 ago</t>
+  </si>
+  <si>
+    <t>18 ago</t>
+  </si>
+  <si>
+    <t>19 ago</t>
+  </si>
+  <si>
+    <t>20 ago</t>
+  </si>
+  <si>
+    <t>21 ago</t>
+  </si>
+  <si>
+    <t>22 ago</t>
+  </si>
+  <si>
+    <t>23 ago</t>
+  </si>
+  <si>
+    <t>Sopa de mazorca</t>
+  </si>
+  <si>
+    <t>Carne desmechada</t>
+  </si>
+  <si>
+    <t>Patacón</t>
+  </si>
+  <si>
+    <t>Ensalada mixta</t>
+  </si>
+  <si>
+    <t>a la vinagreta</t>
+  </si>
+  <si>
+    <t>Arroz con caraota</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco de maíz</t>
+  </si>
+  <si>
+    <t>Carne a la cerveza</t>
+  </si>
+  <si>
+    <t>Cascos de papa dorada</t>
+  </si>
+  <si>
+    <t>Ensalada del sol</t>
+  </si>
+  <si>
+    <t>Arroz al pimentón</t>
+  </si>
+  <si>
+    <t>Sopa de minestrone</t>
+  </si>
+  <si>
+    <t>Pollo mediterráneo</t>
+  </si>
+  <si>
+    <t>Papa a la griega</t>
+  </si>
+  <si>
+    <t>Ensalada primavera</t>
+  </si>
+  <si>
+    <t>Crema de cebolla</t>
+  </si>
+  <si>
+    <t>Rollo de carne</t>
+  </si>
+  <si>
+    <t>En salsa strogonoff</t>
+  </si>
+  <si>
+    <t>Papa al perejil</t>
+  </si>
+  <si>
+    <t>Ensalada de verano</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco de trigo</t>
+  </si>
+  <si>
+    <t>Alitas de pollo a la broaster</t>
+  </si>
+  <si>
+    <t>Papa alemana</t>
+  </si>
+  <si>
+    <t>Ensalada cherry</t>
+  </si>
+  <si>
+    <t>Arroz con alverja</t>
+  </si>
+  <si>
+    <t>Espaguetis mixtos</t>
+  </si>
+  <si>
+    <t>Con pollo y boloñesa</t>
+  </si>
+  <si>
+    <t>Pan francés con ajo</t>
+  </si>
+  <si>
+    <t>Ensalada tropical</t>
+  </si>
+  <si>
+    <t>Papa crisper</t>
+  </si>
+  <si>
+    <t>Churrasco a la plancha</t>
+  </si>
+  <si>
+    <t>Papa a la crema</t>
+  </si>
+  <si>
+    <t>Ensalada roja</t>
+  </si>
+  <si>
+    <t>Arooz blanco</t>
   </si>
 </sst>
 </file>
@@ -666,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -701,14 +713,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -717,14 +729,14 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -733,14 +745,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -749,30 +761,32 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -781,14 +795,14 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -797,32 +811,30 @@
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>49</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -831,14 +843,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -847,14 +859,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -863,14 +875,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -879,14 +891,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -895,14 +907,14 @@
         <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F14" s="4"/>
     </row>
@@ -911,14 +923,14 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F15" s="4"/>
     </row>
@@ -927,14 +939,14 @@
         <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -943,14 +955,14 @@
         <v>12</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -959,30 +971,32 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -991,30 +1005,30 @@
         <v>12</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F21" s="4"/>
     </row>
@@ -1023,32 +1037,30 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>63</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -1057,14 +1069,14 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1073,43 +1085,39 @@
         <v>13</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>10</v>
@@ -1118,16 +1126,18 @@
         <v>15</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>10</v>
@@ -1136,7 +1146,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F28" s="4"/>
     </row>
@@ -1145,7 +1155,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
@@ -1154,7 +1164,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F29" s="4"/>
     </row>
@@ -1163,16 +1173,16 @@
         <v>14</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F30" s="4"/>
     </row>
@@ -1181,7 +1191,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
@@ -1190,7 +1200,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="F31" s="4"/>
     </row>
@@ -1199,7 +1209,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
@@ -1208,16 +1218,18 @@
         <v>20</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F32" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
@@ -1226,7 +1238,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F33" s="4"/>
     </row>
@@ -1235,7 +1247,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
@@ -1244,23 +1256,25 @@
         <v>20</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E35" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F35" s="4"/>
     </row>
@@ -1269,14 +1283,14 @@
         <v>22</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="F36" s="4"/>
     </row>
@@ -1285,14 +1299,14 @@
         <v>22</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -1301,45 +1315,59 @@
         <v>22</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>73</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A399" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C399" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D399" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005E44FE-CDE7-44E5-A1E0-A5F4FEA6F867}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48A9C868-62CC-4931-9F3D-1BF09192E4D2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="79">
   <si>
     <t>Día</t>
   </si>
@@ -131,133 +131,133 @@
     <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
   </si>
   <si>
-    <t>Sopa de mute</t>
-  </si>
-  <si>
-    <t>Arroz al cebollín</t>
-  </si>
-  <si>
-    <t>17 ago</t>
-  </si>
-  <si>
-    <t>18 ago</t>
-  </si>
-  <si>
-    <t>19 ago</t>
-  </si>
-  <si>
-    <t>20 ago</t>
-  </si>
-  <si>
-    <t>21 ago</t>
-  </si>
-  <si>
-    <t>22 ago</t>
-  </si>
-  <si>
-    <t>23 ago</t>
-  </si>
-  <si>
     <t>Sopa de mazorca</t>
   </si>
   <si>
-    <t>Carne desmechada</t>
-  </si>
-  <si>
-    <t>Patacón</t>
-  </si>
-  <si>
-    <t>Ensalada mixta</t>
-  </si>
-  <si>
-    <t>a la vinagreta</t>
-  </si>
-  <si>
-    <t>Arroz con caraota</t>
-  </si>
-  <si>
-    <t>Sopa de cuchuco de maíz</t>
-  </si>
-  <si>
-    <t>Carne a la cerveza</t>
-  </si>
-  <si>
-    <t>Cascos de papa dorada</t>
-  </si>
-  <si>
-    <t>Ensalada del sol</t>
-  </si>
-  <si>
-    <t>Arroz al pimentón</t>
-  </si>
-  <si>
     <t>Sopa de minestrone</t>
   </si>
   <si>
-    <t>Pollo mediterráneo</t>
-  </si>
-  <si>
-    <t>Papa a la griega</t>
-  </si>
-  <si>
     <t>Ensalada primavera</t>
   </si>
   <si>
-    <t>Crema de cebolla</t>
-  </si>
-  <si>
-    <t>Rollo de carne</t>
-  </si>
-  <si>
-    <t>En salsa strogonoff</t>
-  </si>
-  <si>
-    <t>Papa al perejil</t>
-  </si>
-  <si>
-    <t>Ensalada de verano</t>
-  </si>
-  <si>
-    <t>Sopa de cuchuco de trigo</t>
-  </si>
-  <si>
-    <t>Alitas de pollo a la broaster</t>
-  </si>
-  <si>
-    <t>Papa alemana</t>
-  </si>
-  <si>
-    <t>Ensalada cherry</t>
-  </si>
-  <si>
-    <t>Arroz con alverja</t>
-  </si>
-  <si>
-    <t>Espaguetis mixtos</t>
-  </si>
-  <si>
-    <t>Con pollo y boloñesa</t>
-  </si>
-  <si>
-    <t>Pan francés con ajo</t>
-  </si>
-  <si>
-    <t>Ensalada tropical</t>
-  </si>
-  <si>
-    <t>Papa crisper</t>
-  </si>
-  <si>
-    <t>Churrasco a la plancha</t>
-  </si>
-  <si>
-    <t>Papa a la crema</t>
-  </si>
-  <si>
-    <t>Ensalada roja</t>
-  </si>
-  <si>
-    <t>Arooz blanco</t>
+    <t>24 ago</t>
+  </si>
+  <si>
+    <t>25 ago</t>
+  </si>
+  <si>
+    <t>26 ago</t>
+  </si>
+  <si>
+    <t>27 ago</t>
+  </si>
+  <si>
+    <t>28 ago</t>
+  </si>
+  <si>
+    <t>29 ago</t>
+  </si>
+  <si>
+    <t>30 ago</t>
+  </si>
+  <si>
+    <t>Sopa de patacón</t>
+  </si>
+  <si>
+    <t>Carne en bistec</t>
+  </si>
+  <si>
+    <t>Torta de zanahoria</t>
+  </si>
+  <si>
+    <t>Ensalada fantasía</t>
+  </si>
+  <si>
+    <t>Pollo a la cazadora</t>
+  </si>
+  <si>
+    <t>Anillos de cebolla a la orly</t>
+  </si>
+  <si>
+    <t>Arroz verde</t>
+  </si>
+  <si>
+    <t>Bandeja paisa</t>
+  </si>
+  <si>
+    <t>9 acompañamientos</t>
+  </si>
+  <si>
+    <t>Sopa de durena</t>
+  </si>
+  <si>
+    <t>Plátano maduro</t>
+  </si>
+  <si>
+    <t>Verduras calientes</t>
+  </si>
+  <si>
+    <t>Carne de res / Pollo / Chuleta de cerdo</t>
+  </si>
+  <si>
+    <t>Elige tu proteína</t>
+  </si>
+  <si>
+    <t>Crema de ahuyama</t>
+  </si>
+  <si>
+    <t>Pollo gratinado</t>
+  </si>
+  <si>
+    <t>En salsa de ciruelas</t>
+  </si>
+  <si>
+    <t>Papa duquesa</t>
+  </si>
+  <si>
+    <t>Ensalada romana</t>
+  </si>
+  <si>
+    <t>Arroz al perejil</t>
+  </si>
+  <si>
+    <t>Sopa de tortilla de huevo</t>
+  </si>
+  <si>
+    <t>Mojarra frita</t>
+  </si>
+  <si>
+    <t>Patacón con hogao</t>
+  </si>
+  <si>
+    <t>Ensalada con aguacate</t>
+  </si>
+  <si>
+    <t>Arroz con coco</t>
+  </si>
+  <si>
+    <t>Arroz cubano</t>
+  </si>
+  <si>
+    <t>Pollo, res y cerdo</t>
+  </si>
+  <si>
+    <t>Ensalada bellavista</t>
+  </si>
+  <si>
+    <t>Pollo a la vizcaína</t>
+  </si>
+  <si>
+    <t>Copitos de papa al cebollín</t>
+  </si>
+  <si>
+    <t>Ensalada de melón</t>
+  </si>
+  <si>
+    <t>Con vinagreta oriental</t>
+  </si>
+  <si>
+    <t>Arroz con quinoa</t>
   </si>
 </sst>
 </file>
@@ -678,8 +678,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -688,7 +688,7 @@
     <col min="5" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,251 +708,253 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="E12" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="E13" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="D14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="D15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="D16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>41</v>
@@ -960,15 +962,17 @@
       <c r="C17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="E17" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>41</v>
@@ -976,17 +980,19 @@
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="E18" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>41</v>
@@ -994,15 +1000,17 @@
       <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="E19" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>41</v>
@@ -1010,15 +1018,17 @@
       <c r="C20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="E20" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>41</v>
@@ -1026,348 +1036,432 @@
       <c r="C21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="E21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D28" s="3"/>
       <c r="E28" s="4" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D29" s="3"/>
       <c r="E29" s="4" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="4" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D31" s="3"/>
       <c r="E31" s="4" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E36" s="4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E37" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E38" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E39" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F40" s="4"/>
+      <c r="F45" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A405" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C405" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D405" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1378,84 +1472,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
     </row>
-    <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>35</v>
       </c>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48A9C868-62CC-4931-9F3D-1BF09192E4D2}"/>
+  <xr:revisionPtr revIDLastSave="303" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C07EBE3-2B31-4B66-986A-3747116530D4}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="79">
   <si>
     <t>Día</t>
   </si>
@@ -879,7 +879,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>53</v>
@@ -897,7 +897,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>54</v>
@@ -914,9 +914,7 @@
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
@@ -930,9 +928,7 @@
       <c r="C15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
@@ -946,9 +942,7 @@
       <c r="C16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
@@ -963,7 +957,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>55</v>
@@ -981,7 +975,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>58</v>
@@ -1001,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>56</v>
@@ -1019,7 +1013,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>57</v>
@@ -1037,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>8</v>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="303" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C07EBE3-2B31-4B66-986A-3747116530D4}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA9B7DB4-EC11-4D92-AFB2-067C7EE0AB05}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="75">
   <si>
     <t>Día</t>
   </si>
@@ -131,133 +131,121 @@
     <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
   </si>
   <si>
-    <t>Sopa de mazorca</t>
-  </si>
-  <si>
-    <t>Sopa de minestrone</t>
-  </si>
-  <si>
-    <t>Ensalada primavera</t>
-  </si>
-  <si>
-    <t>24 ago</t>
-  </si>
-  <si>
-    <t>25 ago</t>
-  </si>
-  <si>
-    <t>26 ago</t>
-  </si>
-  <si>
-    <t>27 ago</t>
-  </si>
-  <si>
-    <t>28 ago</t>
-  </si>
-  <si>
-    <t>29 ago</t>
-  </si>
-  <si>
-    <t>30 ago</t>
-  </si>
-  <si>
-    <t>Sopa de patacón</t>
-  </si>
-  <si>
-    <t>Carne en bistec</t>
-  </si>
-  <si>
-    <t>Torta de zanahoria</t>
-  </si>
-  <si>
-    <t>Ensalada fantasía</t>
-  </si>
-  <si>
-    <t>Pollo a la cazadora</t>
-  </si>
-  <si>
-    <t>Anillos de cebolla a la orly</t>
-  </si>
-  <si>
-    <t>Arroz verde</t>
-  </si>
-  <si>
-    <t>Bandeja paisa</t>
-  </si>
-  <si>
-    <t>9 acompañamientos</t>
-  </si>
-  <si>
-    <t>Sopa de durena</t>
-  </si>
-  <si>
-    <t>Plátano maduro</t>
-  </si>
-  <si>
-    <t>Verduras calientes</t>
-  </si>
-  <si>
-    <t>Carne de res / Pollo / Chuleta de cerdo</t>
-  </si>
-  <si>
-    <t>Elige tu proteína</t>
-  </si>
-  <si>
-    <t>Crema de ahuyama</t>
-  </si>
-  <si>
-    <t>Pollo gratinado</t>
-  </si>
-  <si>
-    <t>En salsa de ciruelas</t>
-  </si>
-  <si>
-    <t>Papa duquesa</t>
-  </si>
-  <si>
-    <t>Ensalada romana</t>
-  </si>
-  <si>
-    <t>Arroz al perejil</t>
-  </si>
-  <si>
-    <t>Sopa de tortilla de huevo</t>
-  </si>
-  <si>
-    <t>Mojarra frita</t>
-  </si>
-  <si>
-    <t>Patacón con hogao</t>
-  </si>
-  <si>
-    <t>Ensalada con aguacate</t>
-  </si>
-  <si>
-    <t>Arroz con coco</t>
-  </si>
-  <si>
-    <t>Arroz cubano</t>
-  </si>
-  <si>
-    <t>Pollo, res y cerdo</t>
-  </si>
-  <si>
-    <t>Ensalada bellavista</t>
-  </si>
-  <si>
-    <t>Pollo a la vizcaína</t>
-  </si>
-  <si>
-    <t>Copitos de papa al cebollín</t>
-  </si>
-  <si>
-    <t>Ensalada de melón</t>
-  </si>
-  <si>
-    <t>Con vinagreta oriental</t>
-  </si>
-  <si>
     <t>Arroz con quinoa</t>
+  </si>
+  <si>
+    <t>31 ago</t>
+  </si>
+  <si>
+    <t>1 sept</t>
+  </si>
+  <si>
+    <t>2 sept</t>
+  </si>
+  <si>
+    <t>3 sept</t>
+  </si>
+  <si>
+    <t>4 sept</t>
+  </si>
+  <si>
+    <t>5 sept</t>
+  </si>
+  <si>
+    <t>6 sept</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco de cebada</t>
+  </si>
+  <si>
+    <t>Costilla de cerdo en salsa BBQ</t>
+  </si>
+  <si>
+    <t>Papa asada</t>
+  </si>
+  <si>
+    <t>Verduras salteadas</t>
+  </si>
+  <si>
+    <t>Sopa de verduras</t>
+  </si>
+  <si>
+    <t>Pollo a la broaster</t>
+  </si>
+  <si>
+    <t>Papas horneadas al limón</t>
+  </si>
+  <si>
+    <t>Ensalada hawaiana</t>
+  </si>
+  <si>
+    <t>Arroz al cebollín</t>
+  </si>
+  <si>
+    <t>Crema de tomate</t>
+  </si>
+  <si>
+    <t>Tacos de carne desmechada</t>
+  </si>
+  <si>
+    <t>Fríjoles</t>
+  </si>
+  <si>
+    <t>Guacamole - Ensalada pico e gallo</t>
+  </si>
+  <si>
+    <t>Arroz amarillo</t>
+  </si>
+  <si>
+    <t>Sopa de avena</t>
+  </si>
+  <si>
+    <t>Pollo tropical</t>
+  </si>
+  <si>
+    <t>Dedito de queso mozzarella</t>
+  </si>
+  <si>
+    <t>Ensalada florentina</t>
+  </si>
+  <si>
+    <t>Sopa de arracacha</t>
+  </si>
+  <si>
+    <t>Bolitas de res en salsa napolitana</t>
+  </si>
+  <si>
+    <t>Yuca dorada</t>
+  </si>
+  <si>
+    <t>Soufflé de acelgas</t>
+  </si>
+  <si>
+    <t>Pollo a la jardinera</t>
+  </si>
+  <si>
+    <t>Torta de banano</t>
+  </si>
+  <si>
+    <t>Ensalada de pepino cohombro, tomate y zuchinni</t>
+  </si>
+  <si>
+    <t>a la vinagreta</t>
+  </si>
+  <si>
+    <t>Entero</t>
+  </si>
+  <si>
+    <t>Consomé</t>
+  </si>
+  <si>
+    <t>Costilla de res</t>
+  </si>
+  <si>
+    <t>Yuca, plátano y mazorca</t>
+  </si>
+  <si>
+    <t>Guacamole - Arroz blanco</t>
   </si>
 </sst>
 </file>
@@ -713,14 +701,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -729,14 +717,14 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -745,14 +733,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -761,14 +749,14 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -777,7 +765,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>10</v>
@@ -793,14 +781,14 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -809,14 +797,14 @@
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -825,14 +813,14 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -841,14 +829,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -857,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
@@ -873,14 +861,12 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
         <v>53</v>
       </c>
@@ -891,14 +877,12 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
         <v>54</v>
       </c>
@@ -909,13 +893,15 @@
         <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -923,13 +909,15 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -937,266 +925,266 @@
         <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="4" t="s">
         <v>59</v>
       </c>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>62</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E27" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E28" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E29" s="4" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E30" s="4" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E31" s="4" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="F31" s="4"/>
     </row>
@@ -1205,69 +1193,69 @@
         <v>14</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="28" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>8</v>
@@ -1276,73 +1264,63 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
         <v>73</v>
       </c>
@@ -1350,112 +1328,70 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="3"/>
       <c r="D41" s="3"/>
-      <c r="E41" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A42" s="2"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="3"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A43" s="2"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="3"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="4" t="s">
-        <v>75</v>
-      </c>
+      <c r="E43" s="4"/>
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="3"/>
       <c r="D44" s="3"/>
-      <c r="E44" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>77</v>
-      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A45" s="2"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="4" t="s">
-        <v>78</v>
-      </c>
+      <c r="E45" s="4"/>
       <c r="F45" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A405" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C405" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D405" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>
